--- a/changes/545-muzzles.xlsx
+++ b/changes/545-muzzles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-dev\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CAB84C-82C2-4CCA-9D3D-B3B6677ABB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB378CB6-38C0-41CE-ACC6-668970688855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="345" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="556-muzzles" sheetId="1" r:id="rId1"/>
@@ -827,11 +827,11 @@
         <v>700</v>
       </c>
       <c r="N5" s="2">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>16.05</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="R5">
         <f t="shared" si="1"/>
@@ -875,11 +875,11 @@
         <v>400</v>
       </c>
       <c r="N6" s="2">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>16.164999999999999</v>
+        <v>16.265000000000001</v>
       </c>
       <c r="Q6">
         <v>3.4</v>
@@ -1208,11 +1208,11 @@
         <v>750</v>
       </c>
       <c r="N14" s="2">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>16.950000000000003</v>
+        <v>17.05</v>
       </c>
       <c r="Q14">
         <v>4.5856199999999996</v>
@@ -1257,11 +1257,11 @@
         <v>750</v>
       </c>
       <c r="N15" s="2">
-        <v>0.06</v>
+        <v>3.9999999999999994E-2</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>16.850000000000001</v>
+        <v>16.950000000000003</v>
       </c>
       <c r="Q15">
         <v>5.6085599999999998</v>
@@ -1309,11 +1309,11 @@
         <v>750</v>
       </c>
       <c r="N16" s="2">
-        <v>0.06</v>
+        <v>3.9999999999999994E-2</v>
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>17.149999999999999</v>
+        <v>17.25</v>
       </c>
       <c r="Q16">
         <v>4.5856199999999996</v>
@@ -1358,11 +1358,11 @@
         <v>750</v>
       </c>
       <c r="N17" s="2">
-        <v>0.06</v>
+        <v>3.9999999999999994E-2</v>
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>17.350000000000001</v>
+        <v>17.450000000000003</v>
       </c>
       <c r="Q17">
         <v>4.0565100000000003</v>
@@ -1407,11 +1407,11 @@
         <v>750</v>
       </c>
       <c r="N18" s="2">
-        <v>0.05</v>
+        <v>3.0000000000000002E-2</v>
       </c>
       <c r="O18">
         <f t="shared" si="0"/>
-        <v>16.100000000000001</v>
+        <v>16.200000000000003</v>
       </c>
       <c r="Q18">
         <v>5.64</v>
@@ -1456,11 +1456,11 @@
         <v>750</v>
       </c>
       <c r="N19" s="2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="O19">
         <f t="shared" si="0"/>
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="Q19">
         <v>4.4092500000000001</v>
@@ -1505,11 +1505,11 @@
         <v>1000</v>
       </c>
       <c r="N20" s="2">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="O20">
         <f t="shared" si="0"/>
-        <v>17.650000000000002</v>
+        <v>17.75</v>
       </c>
       <c r="Q20">
         <v>4.5150670000000002</v>
@@ -1554,11 +1554,11 @@
         <v>1000</v>
       </c>
       <c r="N21" s="2">
-        <v>0.09</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="O21">
         <f t="shared" si="0"/>
-        <v>16.95</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="Q21">
         <v>3.7037659999999999</v>
